--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_342_R35.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_342_R35.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6725</v>
+        <v>5.5542</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4514</v>
+        <v>5.5011</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2211</v>
+        <v>0.0531</v>
       </c>
       <c r="G2" t="n">
         <v>6.6614</v>
@@ -610,13 +610,13 @@
         <v>3.4793</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4528</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3364</v>
+        <v>-0.2867</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1164</v>
+        <v>-0.2844</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9183</v>
+        <v>2.2592</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8291</v>
+        <v>1.2708</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0892</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>0.7917</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3586</v>
+        <v>1.6994</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8363</v>
+        <v>1.2779</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3261</v>
+        <v>1.82</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3995</v>
+        <v>1.6918</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.07340000000000001</v>
+        <v>0.1282</v>
       </c>
       <c r="G4" t="n">
         <v>0.5518</v>
@@ -766,13 +766,13 @@
         <v>3.2473</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4551</v>
+        <v>-0.9612000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5351</v>
+        <v>-0.1727</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9902</v>
+        <v>-0.7885</v>
       </c>
       <c r="V4" t="n">
         <v>0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7812</v>
+        <v>1.3601</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4779</v>
+        <v>3.124</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6967</v>
+        <v>-1.7639</v>
       </c>
       <c r="G5" t="n">
         <v>0.2099</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0378</v>
+        <v>-0.3833</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3383</v>
+        <v>-0.0156</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3005</v>
+        <v>-0.3677</v>
       </c>
       <c r="V5" t="n">
         <v>0.1418</v>
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2976</v>
+        <v>1.1796</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1645</v>
+        <v>1.0466</v>
       </c>
       <c r="F6" t="n">
         <v>0.133</v>
@@ -922,10 +922,10 @@
         <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0104</v>
+        <v>-1.1283</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1019</v>
+        <v>-0.2199</v>
       </c>
       <c r="U6" t="n">
         <v>-0.9085</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0196</v>
+        <v>0.9935</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8672</v>
+        <v>0.9419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1524</v>
+        <v>0.0516</v>
       </c>
       <c r="G7" t="n">
         <v>0.8064</v>
@@ -1000,13 +1000,13 @@
         <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.8129</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4402</v>
+        <v>-0.3655</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3466</v>
+        <v>-0.4474</v>
       </c>
       <c r="V7" t="n">
         <v>0.5361</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1952</v>
+        <v>-0.5815</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7994</v>
+        <v>-0.2529</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3958</v>
+        <v>-0.3286</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3226</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5685</v>
+        <v>0.0452</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2987</v>
+        <v>0.2478</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. OJELEYE</t>
+          <t>T. CARTER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3046</v>
+        <v>-1.5818</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3989</v>
+        <v>-1.5411</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09420000000000001</v>
+        <v>-0.0407</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2129</v>
+        <v>-1.489</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.8511</v>
+        <v>-1.8403</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3618</v>
+        <v>0.3513</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1478</v>
+        <v>-1.4351</v>
       </c>
       <c r="K9" t="n">
         <v>-1.4719</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0651</v>
+        <v>-0.0539</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3792</v>
+        <v>-0.3684</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6859</v>
+        <v>0.3145</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5371</v>
+        <v>-0.2526</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5375</v>
+        <v>-0.1061</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0004</v>
+        <v>-0.1465</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7886</v>
+        <v>-0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. CARTER</t>
+          <t>S. OJELEYE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8006</v>
+        <v>-1.789</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6591</v>
+        <v>-2.1185</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1415</v>
+        <v>0.3295</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.489</v>
+        <v>-3.2129</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8403</v>
+        <v>-1.8511</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3513</v>
+        <v>-1.3618</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4351</v>
+        <v>-2.1478</v>
       </c>
       <c r="K10" t="n">
         <v>-1.4719</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0368</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0539</v>
+        <v>-1.0651</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3684</v>
+        <v>-0.3792</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3145</v>
+        <v>-0.6859</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4714</v>
+        <v>1.0528</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2473</v>
+        <v>0.2348</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>-0.7886</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2036</v>
+        <v>-2.0446</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7268</v>
+        <v>-1.5342</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4768</v>
+        <v>-0.5104</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7198</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.7165</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5975</v>
+        <v>-0.4048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2781</v>
+        <v>-0.3117</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0905</v>
+        <v>-2.8898</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7254</v>
+        <v>-2.2221</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3652</v>
+        <v>-0.6676</v>
       </c>
       <c r="G12" t="n">
         <v>-4.4221</v>
@@ -1390,13 +1390,13 @@
         <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8676</v>
+        <v>1.0684</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2636</v>
+        <v>0.7668</v>
       </c>
       <c r="U12" t="n">
-        <v>0.604</v>
+        <v>0.3016</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.7268</v>
+        <v>-9.4658</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.6393</v>
+        <v>-7.5463</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0875</v>
+        <v>-1.9195</v>
       </c>
       <c r="G13" t="n">
         <v>-2.125</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0477</v>
+        <v>0.2133</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6642</v>
+        <v>0.4288</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3835</v>
+        <v>-0.2155</v>
       </c>
       <c r="V13" t="n">
         <v>-3.6109</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.306000000000001</v>
+        <v>-5.185899999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.759300000000001</v>
+        <v>-1.638899999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.547</v>
+        <v>-3.5469</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.1994</v>
+        <v>-6.199400000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-2.2511</v>
@@ -1537,22 +1537,22 @@
         <v>-10.0202</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4793</v>
+        <v>3.479299999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.2368</v>
       </c>
       <c r="R14" t="n">
-        <v>19.71599999999999</v>
+        <v>19.716</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8671</v>
+        <v>-0.7468000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8479000000000004</v>
+        <v>1.968</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.714900000000001</v>
+        <v>-2.7148</v>
       </c>
       <c r="V14" t="n">
         <v>-1.719</v>
@@ -1561,7 +1561,7 @@
         <v>6.2118</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.930800000000001</v>
+        <v>-7.9308</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.67</v>
+        <v>4.1709</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3248</v>
+        <v>2.971</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3452</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
         <v>1.3622</v>
@@ -1624,13 +1624,13 @@
         <v>2.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8439</v>
+        <v>0.3449</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6844</v>
+        <v>0.3306</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1595</v>
+        <v>0.0143</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3343</v>
+        <v>3.5867</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6917</v>
+        <v>3.2291</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3574</v>
+        <v>0.3577</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7719</v>
+        <v>3.4253</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1164</v>
+        <v>1.4043</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3446</v>
+        <v>2.021</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1153</v>
+        <v>4.9052</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9312</v>
+        <v>1.4088</v>
       </c>
       <c r="L16" t="n">
-        <v>0.184</v>
+        <v>3.4965</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3434</v>
+        <v>-1.4799</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1852</v>
+        <v>-0.0044</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5286</v>
+        <v>-1.4755</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-4.1751</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>-6.0307</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.632</v>
+        <v>0.5838</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7695</v>
+        <v>0.6018</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1375</v>
+        <v>-0.018</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9304</v>
+        <v>3.7527</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3584</v>
+        <v>3.7527</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2278</v>
+        <v>2.8847</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2291</v>
+        <v>2.984</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0012</v>
+        <v>-0.0993</v>
       </c>
       <c r="G17" t="n">
-        <v>3.4253</v>
+        <v>0.7719</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4043</v>
+        <v>1.1164</v>
       </c>
       <c r="I17" t="n">
-        <v>2.021</v>
+        <v>-0.3446</v>
       </c>
       <c r="J17" t="n">
-        <v>4.9052</v>
+        <v>1.1153</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4088</v>
+        <v>0.9312</v>
       </c>
       <c r="L17" t="n">
-        <v>3.4965</v>
+        <v>0.184</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4799</v>
+        <v>-0.3434</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0044</v>
+        <v>0.1852</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4755</v>
+        <v>-0.5286</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.1751</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.0307</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2249</v>
+        <v>1.1824</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6018</v>
+        <v>1.0618</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3769</v>
+        <v>0.1206</v>
       </c>
       <c r="V17" t="n">
-        <v>3.7527</v>
+        <v>0.9304</v>
       </c>
       <c r="W17" t="n">
-        <v>3.7527</v>
+        <v>3.3584</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1517</v>
+        <v>2.6622</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3247</v>
+        <v>0.4426</v>
       </c>
       <c r="F18" t="n">
-        <v>1.827</v>
+        <v>2.2195</v>
       </c>
       <c r="G18" t="n">
         <v>4.4072</v>
@@ -1858,13 +1858,13 @@
         <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.539</v>
+        <v>-0.0286</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1221</v>
+        <v>0.2401</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6611</v>
+        <v>-0.2686</v>
       </c>
       <c r="V18" t="n">
         <v>-0.7886</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.613</v>
+        <v>1.857</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1678</v>
+        <v>0.1823</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4452</v>
+        <v>1.6747</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4844</v>
+        <v>0.8025</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4442</v>
+        <v>1.3111</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0402</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4665</v>
+        <v>1.9786</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3193</v>
+        <v>1.0118</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1472</v>
+        <v>0.9669</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0179</v>
+        <v>-1.1761</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1249</v>
+        <v>0.2993</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.107</v>
+        <v>-1.4755</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>2.5515</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0312</v>
+        <v>1.0545</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>0.7551</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2675</v>
+        <v>0.2994</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6896</v>
+        <v>1.3777</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5254</v>
+        <v>0.1678</v>
       </c>
       <c r="F20" t="n">
-        <v>1.215</v>
+        <v>1.2099</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8025</v>
+        <v>0.4844</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3111</v>
+        <v>0.4442</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5086000000000001</v>
+        <v>0.0402</v>
       </c>
       <c r="J20" t="n">
-        <v>1.9786</v>
+        <v>0.4665</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0118</v>
+        <v>0.3193</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9669</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1761</v>
+        <v>0.0179</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2993</v>
+        <v>0.1249</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4755</v>
+        <v>-0.107</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5515</v>
+        <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1129</v>
+        <v>-0.2664</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0474</v>
+        <v>-0.2987</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1603</v>
+        <v>0.0323</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0512</v>
+        <v>-0.2855</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0054</v>
+        <v>-1.2413</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0567</v>
+        <v>0.9558</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0594</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0901</v>
+        <v>-0.2467</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1735</v>
+        <v>-0.2743</v>
       </c>
       <c r="V21" t="n">
         <v>0.2525</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9308</v>
+        <v>-1.5982</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.154</v>
+        <v>-0.1116</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7768</v>
+        <v>-1.4866</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.0249</v>
+        <v>-0.9454</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8092</v>
+        <v>-0.7347</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.8341</v>
+        <v>-0.2108</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.191</v>
+        <v>-0.1982</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4319</v>
+        <v>-0.1982</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.6229</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.8339</v>
+        <v>-0.7473</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6227</v>
+        <v>-0.5365</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2112</v>
+        <v>-0.2108</v>
       </c>
       <c r="P22" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7024</v>
+        <v>0.0973</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1968</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5056</v>
+        <v>0.0108</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9349</v>
+        <v>-2.2332</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3475</v>
+        <v>-1.154</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5874</v>
+        <v>-1.0793</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9454</v>
+        <v>-2.0249</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7347</v>
+        <v>0.8092</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2108</v>
+        <v>-2.8341</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.1982</v>
+        <v>-0.191</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1982</v>
+        <v>1.4319</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.6229</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7473</v>
+        <v>-1.8339</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5365</v>
+        <v>-0.6227</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2108</v>
+        <v>-1.2112</v>
       </c>
       <c r="P23" t="n">
         <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2394</v>
+        <v>0.4</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1494</v>
+        <v>0.1968</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0901</v>
+        <v>0.2032</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="24">
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5658</v>
+        <v>-5.3299</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6228</v>
+        <v>-3.3869</v>
       </c>
       <c r="F24" t="n">
         <v>-1.943</v>
@@ -2326,10 +2326,10 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7038</v>
+        <v>-0.4679</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U24" t="n">
         <v>-0.181</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.3061</v>
+        <v>7.0924</v>
       </c>
       <c r="E25" t="n">
-        <v>4.083</v>
+        <v>4.082999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>2.2233</v>
+        <v>3.0094</v>
       </c>
       <c r="G25" t="n">
-        <v>6.199400000000001</v>
+        <v>6.199399999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>2.251099999999999</v>
+        <v>2.2511</v>
       </c>
       <c r="I25" t="n">
         <v>3.948</v>
@@ -2404,19 +2404,19 @@
         <v>16.2368</v>
       </c>
       <c r="S25" t="n">
-        <v>1.867</v>
+        <v>2.6533</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7147</v>
+        <v>2.7148</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8477999999999999</v>
+        <v>-0.06130000000000005</v>
       </c>
       <c r="V25" t="n">
-        <v>1.719</v>
+        <v>1.718999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>8.466900000000001</v>
+        <v>8.466899999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-6.747900000000001</v>
